--- a/EA_list.xlsx
+++ b/EA_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhang\Documents\GitHub\Andrews_CompostMulch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40BA1F55-FED6-4272-A773-F744712C875E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9617307-AB82-41B3-8124-E26A821DFAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{5C8F5324-6E1B-4FFE-BB11-C316667C42A0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="112">
   <si>
     <t xml:space="preserve">Tray_Location </t>
   </si>
@@ -44,9 +44,6 @@
     <t>Sample</t>
   </si>
   <si>
-    <t>standard_LECO</t>
-  </si>
-  <si>
     <t>a1</t>
   </si>
   <si>
@@ -348,6 +345,33 @@
   </si>
   <si>
     <t>5% N</t>
+  </si>
+  <si>
+    <t>3 mg</t>
+  </si>
+  <si>
+    <t>EA_Tray</t>
+  </si>
+  <si>
+    <t>Standard_1</t>
+  </si>
+  <si>
+    <t>Standard_2</t>
+  </si>
+  <si>
+    <t>Standard_3</t>
+  </si>
+  <si>
+    <t>Standard_4</t>
+  </si>
+  <si>
+    <t>Bypass</t>
+  </si>
+  <si>
+    <t>Blank</t>
+  </si>
+  <si>
+    <t>NO_FOIL</t>
   </si>
 </sst>
 </file>
@@ -369,12 +393,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -404,9 +434,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -741,886 +773,1228 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2CD18B3-3D3D-48A2-A640-33733FD1CA54}">
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.7109375" customWidth="1"/>
     <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E1" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1"/>
+        <v>109</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>111</v>
+      </c>
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2</v>
+      </c>
+      <c r="G3" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="H3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.98</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="D5" s="1">
         <v>2</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1">
+      <c r="E5" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="1">
+        <v>4.17</v>
+      </c>
+      <c r="D6" s="1">
         <v>5</v>
       </c>
-      <c r="F3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="E6" s="1">
         <v>5</v>
       </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="1">
+        <v>7.81</v>
+      </c>
+      <c r="D7" s="1">
+        <v>8</v>
+      </c>
+      <c r="E7" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1">
+        <v>3.02</v>
+      </c>
+      <c r="D8" s="1">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1">
         <v>2</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1">
+      <c r="C9" s="1">
+        <v>3.01</v>
+      </c>
+      <c r="D9" s="1">
+        <v>3</v>
+      </c>
+      <c r="E9" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B10" s="1">
+        <v>3</v>
+      </c>
+      <c r="C10" s="1">
+        <v>3.41</v>
+      </c>
+      <c r="D10" s="1">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
+        <v>4</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.71</v>
+      </c>
+      <c r="D11" s="1">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1">
+        <v>5</v>
+      </c>
+      <c r="C12" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="D12" s="1">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1">
         <v>6</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C13" s="1">
+        <v>3.28</v>
+      </c>
+      <c r="D13" s="1">
+        <v>3</v>
+      </c>
+      <c r="E13" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1">
+        <v>7</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.84</v>
+      </c>
+      <c r="D14" s="1">
+        <v>3</v>
+      </c>
+      <c r="E14" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="1">
+        <v>8</v>
+      </c>
+      <c r="C15" s="1">
+        <v>3.16</v>
+      </c>
+      <c r="D15" s="1">
+        <v>3</v>
+      </c>
+      <c r="E15" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="1">
+        <v>9</v>
+      </c>
+      <c r="C16" s="1">
+        <v>3.05</v>
+      </c>
+      <c r="D16" s="1">
+        <v>3</v>
+      </c>
+      <c r="E16" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="1">
+        <v>10</v>
+      </c>
+      <c r="C17" s="1">
+        <v>3.05</v>
+      </c>
+      <c r="D17" s="1">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="1">
+        <v>11</v>
+      </c>
+      <c r="C18" s="1">
+        <v>3.54</v>
+      </c>
+      <c r="D18" s="1">
+        <v>3</v>
+      </c>
+      <c r="E18" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="1">
+        <v>12</v>
+      </c>
+      <c r="C19" s="1">
+        <v>3.43</v>
+      </c>
+      <c r="D19" s="1">
+        <v>3</v>
+      </c>
+      <c r="E19" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="1">
+        <v>13</v>
+      </c>
+      <c r="C20" s="1">
+        <v>3.37</v>
+      </c>
+      <c r="D20" s="1">
+        <v>3</v>
+      </c>
+      <c r="E20" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="1">
+        <v>14</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.97</v>
+      </c>
+      <c r="D21" s="1">
+        <v>3</v>
+      </c>
+      <c r="E21" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="1">
+        <v>15</v>
+      </c>
+      <c r="C22" s="1">
+        <v>3.13</v>
+      </c>
+      <c r="D22" s="1">
+        <v>3</v>
+      </c>
+      <c r="E22" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="1">
+        <v>16</v>
+      </c>
+      <c r="C23" s="1">
+        <v>3.48</v>
+      </c>
+      <c r="D23" s="1">
+        <v>3</v>
+      </c>
+      <c r="E23" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="1">
+        <v>17</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.61</v>
+      </c>
+      <c r="D24" s="1">
+        <v>3</v>
+      </c>
+      <c r="E24" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="1">
+        <v>18</v>
+      </c>
+      <c r="C25" s="1">
+        <v>3.34</v>
+      </c>
+      <c r="D25" s="1">
+        <v>3</v>
+      </c>
+      <c r="E25" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="1">
+        <v>19</v>
+      </c>
+      <c r="C26" s="1">
+        <v>3.04</v>
+      </c>
+      <c r="D26" s="1">
+        <v>3</v>
+      </c>
+      <c r="E26" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="1">
+        <v>20</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.84</v>
+      </c>
+      <c r="D27" s="1">
+        <v>3</v>
+      </c>
+      <c r="E27" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="1">
+        <v>21</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2.95</v>
+      </c>
+      <c r="D28" s="1">
+        <v>3</v>
+      </c>
+      <c r="E28" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="1">
+        <v>22</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="D29" s="1">
+        <v>3</v>
+      </c>
+      <c r="E29" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="1">
+        <v>23</v>
+      </c>
+      <c r="C30" s="1">
+        <v>3.04</v>
+      </c>
+      <c r="D30" s="1">
+        <v>3</v>
+      </c>
+      <c r="E30" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="1">
+        <v>24</v>
+      </c>
+      <c r="C31" s="1">
+        <v>3.43</v>
+      </c>
+      <c r="D31" s="1">
+        <v>3</v>
+      </c>
+      <c r="E31" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="1">
+        <v>25</v>
+      </c>
+      <c r="C32" s="1">
+        <v>3.31</v>
+      </c>
+      <c r="D32" s="1">
+        <v>3</v>
+      </c>
+      <c r="E32" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="1">
+        <v>26</v>
+      </c>
+      <c r="C33" s="1">
+        <v>3.38</v>
+      </c>
+      <c r="D33" s="1">
+        <v>3</v>
+      </c>
+      <c r="E33" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="1">
+        <v>27</v>
+      </c>
+      <c r="C34" s="1">
+        <v>3.14</v>
+      </c>
+      <c r="D34" s="1">
+        <v>3</v>
+      </c>
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="1">
+        <v>28</v>
+      </c>
+      <c r="C35" s="1">
+        <v>3.45</v>
+      </c>
+      <c r="D35" s="1">
+        <v>3</v>
+      </c>
+      <c r="E35" s="1">
         <v>2</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="1">
+        <v>29</v>
+      </c>
+      <c r="C36" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="D36" s="1">
+        <v>3</v>
+      </c>
+      <c r="E36" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="1">
+        <v>30</v>
+      </c>
+      <c r="C37" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="D37" s="1">
+        <v>3</v>
+      </c>
+      <c r="E37" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1.24</v>
+      </c>
+      <c r="D38" s="1">
+        <v>2</v>
+      </c>
+      <c r="E38" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="1">
+        <v>31</v>
+      </c>
+      <c r="C39" s="1">
+        <v>3.06</v>
+      </c>
+      <c r="D39" s="1">
+        <v>3</v>
+      </c>
+      <c r="E39" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="1">
+        <v>32</v>
+      </c>
+      <c r="C40" s="1">
+        <v>3.42</v>
+      </c>
+      <c r="D40" s="1">
+        <v>3</v>
+      </c>
+      <c r="E40" s="1">
         <v>7</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="1">
+        <v>33</v>
+      </c>
+      <c r="C41" s="1">
+        <v>3.43</v>
+      </c>
+      <c r="D41" s="1">
+        <v>3</v>
+      </c>
+      <c r="E41" s="1">
         <v>8</v>
       </c>
-      <c r="B7" s="1">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="1">
+        <v>34</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2.76</v>
+      </c>
+      <c r="D42" s="1">
+        <v>3</v>
+      </c>
+      <c r="E42" s="1">
         <v>9</v>
       </c>
-      <c r="B8" s="1">
-        <v>2</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="1">
+        <v>35</v>
+      </c>
+      <c r="C43" s="1">
+        <v>2.72</v>
+      </c>
+      <c r="D43" s="1">
+        <v>3</v>
+      </c>
+      <c r="E43" s="1">
         <v>10</v>
       </c>
-      <c r="B9" s="1">
-        <v>3</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" s="1">
+        <v>36</v>
+      </c>
+      <c r="C44" s="1">
+        <v>3.17</v>
+      </c>
+      <c r="D44" s="1">
+        <v>3</v>
+      </c>
+      <c r="E44" s="1">
         <v>11</v>
       </c>
-      <c r="B10" s="1">
-        <v>4</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="3">
+        <v>37</v>
+      </c>
+      <c r="C45" s="1">
+        <v>3.25</v>
+      </c>
+      <c r="D45" s="1">
+        <v>3</v>
+      </c>
+      <c r="E45" s="1">
         <v>12</v>
       </c>
-      <c r="B11" s="1">
-        <v>5</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="1">
-        <v>6</v>
-      </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="1">
-        <v>7</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="1">
-        <v>8</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="1">
-        <v>9</v>
-      </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="1">
-        <v>10</v>
-      </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="1">
-        <v>11</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="1">
-        <v>12</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="1">
-        <v>13</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="1">
-        <v>14</v>
-      </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="1">
-        <v>15</v>
-      </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="1">
-        <v>16</v>
-      </c>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="1">
-        <v>17</v>
-      </c>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="1">
-        <v>18</v>
-      </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="1">
-        <v>19</v>
-      </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="1">
-        <v>20</v>
-      </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="1">
-        <v>21</v>
-      </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" s="1">
-        <v>22</v>
-      </c>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" s="1">
-        <v>23</v>
-      </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" s="1">
-        <v>24</v>
-      </c>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31" s="1">
-        <v>25</v>
-      </c>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32" s="1">
-        <v>26</v>
-      </c>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" s="1">
-        <v>27</v>
-      </c>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" s="1">
-        <v>28</v>
-      </c>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" s="1">
-        <v>29</v>
-      </c>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="1">
-        <v>30</v>
-      </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="1">
-        <v>31</v>
-      </c>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="1">
-        <v>32</v>
-      </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="1">
-        <v>33</v>
-      </c>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="1">
-        <v>34</v>
-      </c>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="1">
-        <v>35</v>
-      </c>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="1">
-        <v>36</v>
-      </c>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B43" s="1">
-        <v>37</v>
-      </c>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B44" s="1">
-        <v>38</v>
-      </c>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="1">
-        <v>39</v>
-      </c>
-      <c r="C46" s="1"/>
+      <c r="B46" s="3">
+        <v>38</v>
+      </c>
+      <c r="C46" s="1">
+        <v>2.72</v>
+      </c>
       <c r="D46" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E46" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B47" s="1">
-        <v>40</v>
-      </c>
-      <c r="C47" s="1"/>
+        <v>39</v>
+      </c>
+      <c r="C47" s="1">
+        <v>3.46</v>
+      </c>
       <c r="D47" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E47" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B48" s="1">
-        <v>41</v>
-      </c>
-      <c r="C48" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="C48" s="1">
+        <v>3.21</v>
+      </c>
       <c r="D48" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E48" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B49" s="1">
-        <v>42</v>
-      </c>
-      <c r="C49" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="C49" s="1">
+        <v>3.48</v>
+      </c>
       <c r="D49" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E49" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B50" s="1">
-        <v>43</v>
-      </c>
-      <c r="C50" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="C50" s="1">
+        <v>3.3</v>
+      </c>
       <c r="D50" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E50" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B51" s="1">
-        <v>44</v>
-      </c>
-      <c r="C51" s="1"/>
+        <v>43</v>
+      </c>
+      <c r="C51" s="1">
+        <v>2.5499999999999998</v>
+      </c>
       <c r="D51" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E51" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B52" s="1">
-        <v>45</v>
-      </c>
-      <c r="C52" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="C52" s="1">
+        <v>3.31</v>
+      </c>
       <c r="D52" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E52" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B53" s="1">
-        <v>46</v>
-      </c>
-      <c r="C53" s="1"/>
+        <v>45</v>
+      </c>
+      <c r="C53" s="1">
+        <v>2.97</v>
+      </c>
       <c r="D53" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E53" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B54" s="1">
-        <v>47</v>
-      </c>
-      <c r="C54" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="C54" s="1">
+        <v>3.38</v>
+      </c>
       <c r="D54" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E54" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B55" s="1">
-        <v>48</v>
-      </c>
-      <c r="C55" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="C55" s="1">
+        <v>3.5</v>
+      </c>
       <c r="D55" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E55" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B56" s="1">
-        <v>49</v>
-      </c>
-      <c r="C56" s="1"/>
+        <v>48</v>
+      </c>
+      <c r="C56" s="1">
+        <v>2.85</v>
+      </c>
       <c r="D56" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E56" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B57" s="1">
-        <v>50</v>
-      </c>
-      <c r="C57" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="C57" s="1">
+        <v>3.05</v>
+      </c>
       <c r="D57" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E57" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B58" s="1">
-        <v>51</v>
-      </c>
-      <c r="C58" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="C58" s="1">
+        <v>3.23</v>
+      </c>
       <c r="D58" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E58" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B59" s="1">
-        <v>52</v>
-      </c>
-      <c r="C59" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="C59" s="1">
+        <v>3.18</v>
+      </c>
       <c r="D59" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E59" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B60" s="1">
-        <v>53</v>
-      </c>
-      <c r="C60" s="1"/>
+        <v>52</v>
+      </c>
+      <c r="C60" s="1">
+        <v>3.07</v>
+      </c>
       <c r="D60" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E60" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B61" s="1">
-        <v>54</v>
-      </c>
-      <c r="C61" s="1"/>
+        <v>53</v>
+      </c>
+      <c r="C61" s="1">
+        <v>2.56</v>
+      </c>
       <c r="D61" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E61" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B62" s="1">
-        <v>55</v>
-      </c>
-      <c r="C62" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="C62" s="1">
+        <v>3.28</v>
+      </c>
       <c r="D62" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E62" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B63" s="1">
-        <v>56</v>
-      </c>
-      <c r="C63" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="C63" s="1">
+        <v>3.43</v>
+      </c>
       <c r="D63" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E63" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>64</v>
       </c>
       <c r="B64" s="1">
-        <v>57</v>
-      </c>
-      <c r="C64" s="1"/>
+        <v>56</v>
+      </c>
+      <c r="C64" s="1">
+        <v>3.1</v>
+      </c>
       <c r="D64" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E64" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B65" s="1">
-        <v>58</v>
-      </c>
-      <c r="C65" s="1"/>
+        <v>57</v>
+      </c>
+      <c r="C65" s="1">
+        <v>3.25</v>
+      </c>
       <c r="D65" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E65" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B66" s="1">
+        <v>58</v>
+      </c>
+      <c r="C66" s="1">
+        <v>3.49</v>
+      </c>
+      <c r="D66" s="1">
+        <v>3</v>
+      </c>
+      <c r="E66" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B67" s="1">
         <v>59</v>
       </c>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C67" s="1">
+        <v>3.07</v>
+      </c>
+      <c r="D67" s="1">
+        <v>3</v>
+      </c>
+      <c r="E67" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>80</v>
       </c>
@@ -1708,11 +2082,6 @@
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
